--- a/reports/hours_02-2026.xlsx
+++ b/reports/hours_02-2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G203"/>
+  <dimension ref="A1:G205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="F2" t="n">
+        <v>0.25</v>
       </c>
       <c r="G2" t="inlineStr"/>
     </row>
@@ -512,10 +510,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F3" t="n">
+        <v>0.5</v>
       </c>
       <c r="G3" t="inlineStr"/>
     </row>
@@ -545,10 +541,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F4" t="n">
+        <v>1.5</v>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
@@ -578,10 +572,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F5" t="n">
+        <v>1.5</v>
       </c>
       <c r="G5" t="inlineStr"/>
     </row>
@@ -611,10 +603,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F6" t="n">
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
@@ -644,10 +634,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F7" t="n">
+        <v>2.5</v>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
@@ -677,10 +665,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F8" t="n">
+        <v>0.5</v>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
@@ -710,10 +696,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F9" t="n">
+        <v>0.75</v>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
@@ -743,10 +727,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F10" t="n">
+        <v>2.5</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
@@ -776,10 +758,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F11" t="n">
+        <v>1.5</v>
       </c>
       <c r="G11" t="inlineStr"/>
     </row>
@@ -809,10 +789,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F12" t="n">
+        <v>0.75</v>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
@@ -842,10 +820,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F13" t="n">
+        <v>0.5</v>
       </c>
       <c r="G13" t="inlineStr"/>
     </row>
@@ -875,10 +851,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F14" t="n">
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
@@ -908,10 +882,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F15" t="n">
+        <v>2.5</v>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
@@ -941,10 +913,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F16" t="n">
+        <v>0.5</v>
       </c>
       <c r="G16" t="inlineStr"/>
     </row>
@@ -974,10 +944,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F17" t="n">
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr"/>
     </row>
@@ -1007,10 +975,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F18" t="n">
+        <v>0.75</v>
       </c>
       <c r="G18" t="inlineStr"/>
     </row>
@@ -1040,10 +1006,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F19" t="n">
+        <v>0.5</v>
       </c>
       <c r="G19" t="inlineStr"/>
     </row>
@@ -1073,10 +1037,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F20" t="n">
+        <v>0.75</v>
       </c>
       <c r="G20" t="inlineStr"/>
     </row>
@@ -1106,10 +1068,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
+      <c r="F21" t="n">
+        <v>1.25</v>
       </c>
       <c r="G21" t="inlineStr"/>
     </row>
@@ -1139,10 +1099,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F22" t="n">
+        <v>1.5</v>
       </c>
       <c r="G22" t="inlineStr"/>
     </row>
@@ -1172,10 +1130,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F23" t="n">
+        <v>1.5</v>
       </c>
       <c r="G23" t="inlineStr"/>
     </row>
@@ -1205,10 +1161,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F24" t="n">
+        <v>1.5</v>
       </c>
       <c r="G24" t="inlineStr"/>
     </row>
@@ -1238,10 +1192,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F25" t="n">
+        <v>0.75</v>
       </c>
       <c r="G25" t="inlineStr"/>
     </row>
@@ -1271,10 +1223,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F26" t="n">
+        <v>2</v>
       </c>
       <c r="G26" t="inlineStr"/>
     </row>
@@ -1304,10 +1254,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F27" t="n">
+        <v>1.5</v>
       </c>
       <c r="G27" t="inlineStr"/>
     </row>
@@ -1337,10 +1285,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F28" t="n">
+        <v>0.5</v>
       </c>
       <c r="G28" t="inlineStr"/>
     </row>
@@ -1370,10 +1316,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F29" t="n">
+        <v>0.75</v>
       </c>
       <c r="G29" t="inlineStr"/>
     </row>
@@ -1403,10 +1347,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F30" t="n">
+        <v>1.5</v>
       </c>
       <c r="G30" t="inlineStr"/>
     </row>
@@ -1436,10 +1378,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F31" t="n">
+        <v>0.75</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1469,10 +1409,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F32" t="n">
+        <v>0.5</v>
       </c>
       <c r="G32" t="inlineStr"/>
     </row>
@@ -1502,10 +1440,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F33" t="n">
+        <v>0.75</v>
       </c>
       <c r="G33" t="inlineStr"/>
     </row>
@@ -1535,10 +1471,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F34" t="n">
+        <v>1.5</v>
       </c>
       <c r="G34" t="inlineStr"/>
     </row>
@@ -1568,10 +1502,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F35" t="n">
+        <v>0.5</v>
       </c>
       <c r="G35" t="inlineStr"/>
     </row>
@@ -1601,10 +1533,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F36" t="n">
+        <v>1.5</v>
       </c>
       <c r="G36" t="inlineStr"/>
     </row>
@@ -1634,10 +1564,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F37" t="n">
+        <v>1.5</v>
       </c>
       <c r="G37" t="inlineStr"/>
     </row>
@@ -1667,10 +1595,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F38" t="n">
+        <v>0.5</v>
       </c>
       <c r="G38" t="inlineStr"/>
     </row>
@@ -1700,10 +1626,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F39" t="n">
+        <v>0.5</v>
       </c>
       <c r="G39" t="inlineStr"/>
     </row>
@@ -1733,10 +1657,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F40" t="n">
+        <v>1.5</v>
       </c>
       <c r="G40" t="inlineStr"/>
     </row>
@@ -1766,10 +1688,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F41" t="n">
+        <v>0.75</v>
       </c>
       <c r="G41" t="inlineStr"/>
     </row>
@@ -1799,10 +1719,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="F42" t="n">
+        <v>1.75</v>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
@@ -1832,10 +1750,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F43" t="n">
+        <v>0.5</v>
       </c>
       <c r="G43" t="inlineStr"/>
     </row>
@@ -1865,10 +1781,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F44" t="n">
+        <v>0.75</v>
       </c>
       <c r="G44" t="inlineStr"/>
     </row>
@@ -1898,10 +1812,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F45" t="n">
+        <v>0.5</v>
       </c>
       <c r="G45" t="inlineStr"/>
     </row>
@@ -1931,10 +1843,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="F46" t="n">
+        <v>0.25</v>
       </c>
       <c r="G46" t="inlineStr"/>
     </row>
@@ -1964,10 +1874,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F47" t="n">
+        <v>0.5</v>
       </c>
       <c r="G47" t="inlineStr"/>
     </row>
@@ -1997,10 +1905,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F48" t="n">
+        <v>0.75</v>
       </c>
       <c r="G48" t="inlineStr"/>
     </row>
@@ -2030,10 +1936,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F49" t="n">
+        <v>0.5</v>
       </c>
       <c r="G49" t="inlineStr"/>
     </row>
@@ -2063,10 +1967,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F50" t="n">
+        <v>2</v>
       </c>
       <c r="G50" t="inlineStr"/>
     </row>
@@ -2096,10 +1998,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
+      <c r="F51" t="n">
+        <v>1.25</v>
       </c>
       <c r="G51" t="inlineStr"/>
     </row>
@@ -2129,10 +2029,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F52" t="n">
+        <v>0.5</v>
       </c>
       <c r="G52" t="inlineStr"/>
     </row>
@@ -2162,10 +2060,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="F53" t="n">
+        <v>0.25</v>
       </c>
       <c r="G53" t="inlineStr"/>
     </row>
@@ -2195,10 +2091,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F54" t="n">
+        <v>2</v>
       </c>
       <c r="G54" t="inlineStr"/>
     </row>
@@ -2228,10 +2122,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F55" t="n">
+        <v>1</v>
       </c>
       <c r="G55" t="inlineStr"/>
     </row>
@@ -2261,10 +2153,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F56" t="n">
+        <v>0.75</v>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
@@ -2294,10 +2184,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F57" t="n">
+        <v>1</v>
       </c>
       <c r="G57" t="inlineStr"/>
     </row>
@@ -2327,10 +2215,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F58" t="n">
+        <v>1.5</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -2360,10 +2246,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F59" t="n">
+        <v>1</v>
       </c>
       <c r="G59" t="inlineStr"/>
     </row>
@@ -2393,10 +2277,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F60" t="n">
+        <v>3</v>
       </c>
       <c r="G60" t="inlineStr"/>
     </row>
@@ -2426,10 +2308,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F61" t="n">
+        <v>0.5</v>
       </c>
       <c r="G61" t="inlineStr"/>
     </row>
@@ -2459,10 +2339,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F62" t="n">
+        <v>1.5</v>
       </c>
       <c r="G62" t="inlineStr"/>
     </row>
@@ -2492,10 +2370,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F63" t="n">
+        <v>0.75</v>
       </c>
       <c r="G63" t="inlineStr"/>
     </row>
@@ -2525,10 +2401,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F64" t="n">
+        <v>1.5</v>
       </c>
       <c r="G64" t="inlineStr"/>
     </row>
@@ -2558,10 +2432,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F65" t="n">
+        <v>1.5</v>
       </c>
       <c r="G65" t="inlineStr"/>
     </row>
@@ -2591,10 +2463,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F66" t="n">
+        <v>1.5</v>
       </c>
       <c r="G66" t="inlineStr"/>
     </row>
@@ -2624,10 +2494,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F67" t="n">
+        <v>0.75</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -2657,10 +2525,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F68" t="n">
+        <v>0.75</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
@@ -2690,10 +2556,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F69" t="n">
+        <v>1</v>
       </c>
       <c r="G69" t="inlineStr"/>
     </row>
@@ -2723,10 +2587,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F70" t="n">
+        <v>0.75</v>
       </c>
       <c r="G70" t="inlineStr"/>
     </row>
@@ -2756,10 +2618,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F71" t="n">
+        <v>0.5</v>
       </c>
       <c r="G71" t="inlineStr"/>
     </row>
@@ -2789,10 +2649,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F72" t="n">
+        <v>1</v>
       </c>
       <c r="G72" t="inlineStr"/>
     </row>
@@ -2804,17 +2662,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>עקיבא איגר</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>רוטשילד 73</t>
+          <t>רוכשים</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>הסכם שכירות אלה בן אהרון</t>
+          <t>מכתב מענה דירה 27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2822,10 +2680,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F73" t="n">
+        <v>0.5</v>
       </c>
       <c r="G73" t="inlineStr"/>
     </row>
@@ -2837,17 +2693,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>משאבי שדה</t>
+          <t>רוטשילד 73</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>הסכם ביטול</t>
+          <t>הסכם שכירות אלה בן אהרון</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2855,10 +2711,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F74" t="n">
+        <v>1</v>
       </c>
       <c r="G74" t="inlineStr"/>
     </row>
@@ -2875,12 +2729,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>תל חנן</t>
+          <t>משאבי שדה</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>מענה לרמ"י בענין העברת הזכויות</t>
+          <t>הסכם ביטול</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2888,10 +2742,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="F75" t="n">
+        <v>0.75</v>
       </c>
       <c r="G75" t="inlineStr"/>
     </row>
@@ -2903,17 +2755,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>עודד מרגלית</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>בית הטקסטיל</t>
+          <t>תל חנן</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>שיחה עו"ד ארז והתכתבות נווה</t>
+          <t>מענה לרמ"י בענין העברת הזכויות</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2921,10 +2773,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F76" t="n">
+        <v>0.25</v>
       </c>
       <c r="G76" t="inlineStr"/>
     </row>
@@ -2936,17 +2786,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>אקרשטיין</t>
+          <t>עודד מרגלית</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>העברת זכויות</t>
+          <t>בית הטקסטיל</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>התכתבות רמ"י ושיחות מרחב צפון</t>
+          <t>שיחה עו"ד ארז והתכתבות נווה</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2954,32 +2804,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F77" t="n">
+        <v>0.75</v>
       </c>
       <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09.02.2026</t>
+          <t>08.02.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>אקרשטיין</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>בית נועם</t>
+          <t>העברת זכויות</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ישיבה שאדיה לענין השלמת קרקע</t>
+          <t>התכתבות רמ"י ושיחות מרחב צפון</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2987,10 +2835,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="F78" t="n">
+        <v>0.5</v>
       </c>
       <c r="G78" t="inlineStr"/>
     </row>
@@ -3002,17 +2848,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>דימונה</t>
+          <t>בית נועם</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ישיבה מרחב דרום לענין הקניית הבעלות</t>
+          <t>ישיבה שאדיה לענין השלמת קרקע</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3020,10 +2866,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F79" t="n">
+        <v>4.5</v>
       </c>
       <c r="G79" t="inlineStr"/>
     </row>
@@ -3040,7 +2884,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>דלרום</t>
+          <t>דימונה</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3053,10 +2897,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F80" t="n">
+        <v>2</v>
       </c>
       <c r="G80" t="inlineStr"/>
     </row>
@@ -3073,12 +2915,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>עין יהב</t>
+          <t>דלרום</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>הארכת חוזה חכירה והעברת זכויות - ישיבה סוניה מרחב דרום</t>
+          <t>ישיבה מרחב דרום לענין הקניית הבעלות</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3086,10 +2928,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F81" t="n">
+        <v>2</v>
       </c>
       <c r="G81" t="inlineStr"/>
     </row>
@@ -3101,17 +2941,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>קניון דרורים</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>שוטף</t>
+          <t>עין יהב</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>רמי מרכז לצורך קידום הבקשה להיתר + מסמכים לשמוליק</t>
+          <t>הארכת חוזה חכירה והעברת זכויות - ישיבה סוניה מרחב דרום</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3119,10 +2959,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F82" t="n">
+        <v>2</v>
       </c>
       <c r="G82" t="inlineStr"/>
     </row>
@@ -3134,17 +2972,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>קניון דרורים</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>רמת השרון</t>
+          <t>שוטף</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>בקשה לסריקת התיק רמ"י מרכז</t>
+          <t>רמי מרכז לצורך קידום הבקשה להיתר + מסמכים לשמוליק</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3152,10 +2990,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F83" t="n">
+        <v>1.5</v>
       </c>
       <c r="G83" t="inlineStr"/>
     </row>
@@ -3167,17 +3003,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>שמשון זליג</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>הארכת תקופת בניה</t>
+          <t>רמת השרון</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>רמ"י מרכז לקבלת מסמכים בתיק</t>
+          <t>בקשה לסריקת התיק רמ"י מרכז</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3185,10 +3021,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F84" t="n">
+        <v>0.5</v>
       </c>
       <c r="G84" t="inlineStr"/>
     </row>
@@ -3200,17 +3034,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>שמשון זליג</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>נחשון</t>
+          <t>הארכת תקופת בניה</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>הכנת מסמכים לפי פגישה ברמ"י</t>
+          <t>רמ"י מרכז לקבלת מסמכים בתיק</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3218,10 +3052,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F85" t="n">
+        <v>0.75</v>
       </c>
       <c r="G85" t="inlineStr"/>
     </row>
@@ -3233,17 +3065,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>בראבו</t>
+          <t>נחשון</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>תיקונים להסכם שכירות</t>
+          <t>הכנת מסמכים לפי פגישה ברמ"י</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3251,10 +3083,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F86" t="n">
+        <v>1.5</v>
       </c>
       <c r="G86" t="inlineStr"/>
     </row>
@@ -3266,17 +3096,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>עתירה מינהלית</t>
+          <t>בראבו</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>טיפול בעתירה</t>
+          <t>תיקונים להסכם שכירות</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3284,10 +3114,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F87" t="n">
+        <v>1.5</v>
       </c>
       <c r="G87" t="inlineStr"/>
     </row>
@@ -3299,17 +3127,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>שיכון עובדים</t>
+          <t>עתירה מינהלית</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>טיפול בקבלת אישור עיריה</t>
+          <t>טיפול בעתירה</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3317,32 +3145,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F88" t="n">
+        <v>1</v>
       </c>
       <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10.02.2026</t>
+          <t>09.02.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>בית אלבה</t>
+          <t>שיכון עובדים</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>הכנה לדיון בהשגה + שיחת הכנה</t>
+          <t>טיפול בקבלת אישור עיריה</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3350,10 +3176,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F89" t="n">
+        <v>0.5</v>
       </c>
       <c r="G89" t="inlineStr"/>
     </row>
@@ -3365,17 +3189,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>סוויצאפ</t>
+          <t>בית אלבה</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>שיחת זום ובדיקה הוראות הסכם</t>
+          <t>הכנה לדיון בהשגה + שיחת הכנה</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3383,10 +3207,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F90" t="n">
+        <v>2.5</v>
       </c>
       <c r="G90" t="inlineStr"/>
     </row>
@@ -3398,17 +3220,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>כפיר דהן</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>מכירה כדורי</t>
+          <t>סוויצאפ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>שיחת זום + תיקון טיוטא</t>
+          <t>שיחת זום ובדיקה הוראות הסכם</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3416,10 +3238,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F91" t="n">
+        <v>1.5</v>
       </c>
       <c r="G91" t="inlineStr"/>
     </row>
@@ -3431,17 +3251,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>נייר חדרה</t>
+          <t>כפיר דהן</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>או פי סי</t>
+          <t>מכירה כדורי</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>שיחה לענין כתב שיפוי היטל השבחה ותיקון טיוטא</t>
+          <t>שיחת זום + תיקון טיוטא</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3449,10 +3269,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F92" t="n">
+        <v>2.25</v>
       </c>
       <c r="G92" t="inlineStr"/>
     </row>
@@ -3464,17 +3282,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>נייר חדרה</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>עתירה מינהלית</t>
+          <t>או פי סי</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>בקשה לתיקון העתירה</t>
+          <t>שיחה לענין כתב שיפוי היטל השבחה ותיקון טיוטא</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3482,10 +3300,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
+      <c r="F93" t="n">
+        <v>1.5</v>
       </c>
       <c r="G93" t="inlineStr"/>
     </row>
@@ -3497,17 +3313,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>עודד מרגלית</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>בית הטקסטיל</t>
+          <t>עתירה מינהלית</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>תיקון טיוטא</t>
+          <t>בקשה לתיקון העתירה</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3515,32 +3331,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F94" t="n">
+        <v>3.5</v>
       </c>
       <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>10.02.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>עודד מרגלית</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>רוטשילד 73</t>
+          <t>בית הטקסטיל</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>שיחת זום בענין שכירות אלה + תביעה ג'ו בייקרי</t>
+          <t>תיקון טיוטא</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3548,10 +3362,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F95" t="n">
+        <v>2.5</v>
       </c>
       <c r="G95" t="inlineStr"/>
     </row>
@@ -3563,17 +3375,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>עודד מרגלית</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>בית הטקסטיל</t>
+          <t>רוטשילד 73</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ישיבה פנימית בזום</t>
+          <t>שיחת זום בענין שכירות אלה + תביעה ג'ו בייקרי</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3581,10 +3393,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F96" t="n">
+        <v>1</v>
       </c>
       <c r="G96" t="inlineStr"/>
     </row>
@@ -3596,17 +3406,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>עודד מרגלית</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>מבשרת ציון</t>
+          <t>בית הטקסטיל</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>דיון שני בהתנגדויות</t>
+          <t>ישיבה פנימית בזום</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3614,10 +3424,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F97" t="n">
+        <v>1</v>
       </c>
       <c r="G97" t="inlineStr"/>
     </row>
@@ -3629,17 +3437,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>אגירה</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>עין כרמל</t>
+          <t>מבשרת ציון</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>פגישת זום צדדים</t>
+          <t>דיון שני בהתנגדויות</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3647,10 +3455,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
+      <c r="F98" t="n">
+        <v>0.75</v>
       </c>
       <c r="G98" t="inlineStr"/>
     </row>
@@ -3662,17 +3468,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>אגירה</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>חניון רוטשילד</t>
+          <t>עין כרמל</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>שיחת זום להסכם שכירות ותיקונים לטיוטא</t>
+          <t>פגישת זום צדדים</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3680,10 +3486,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F99" t="n">
+        <v>1.25</v>
       </c>
       <c r="G99" t="inlineStr"/>
     </row>
@@ -3700,12 +3504,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>סוויצאפ</t>
+          <t>חניון רוטשילד</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>בדיקת נתונים מהסכמי שכירות</t>
+          <t>שיחת זום להסכם שכירות ותיקונים לטיוטא</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3713,10 +3517,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F100" t="n">
+        <v>1.5</v>
       </c>
       <c r="G100" t="inlineStr"/>
     </row>
@@ -3728,17 +3530,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>עתירה מינהלית</t>
+          <t>סוויצאפ</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>תיקונים לבקשה לתיקון העתירה</t>
+          <t>בדיקת נתונים מהסכמי שכירות</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3746,10 +3548,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F101" t="n">
+        <v>1</v>
       </c>
       <c r="G101" t="inlineStr"/>
     </row>
@@ -3766,12 +3566,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>חלקה 68</t>
+          <t>עתירה מינהלית</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>הסכם דוראל</t>
+          <t>תיקונים לבקשה לתיקון העתירה</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3779,10 +3579,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F102" t="n">
+        <v>1.5</v>
       </c>
       <c r="G102" t="inlineStr"/>
     </row>
@@ -3794,17 +3592,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>רוחמה 24</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>קוצאי</t>
+          <t>חלקה 68</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>הסכם פשרה שיחה קוצאי ותיקונים</t>
+          <t>הסכם דוראל</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3812,32 +3610,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
+      <c r="F103" t="n">
+        <v>1</v>
       </c>
       <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>12.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>רוחמה 24</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>אלבה</t>
+          <t>קוצאי</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>דיון בהשגה במסמ"ק + הכנה</t>
+          <t>הסכם פשרה שיחה קוצאי ותיקונים</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3845,10 +3641,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
+      <c r="F104" t="n">
+        <v>1.25</v>
       </c>
       <c r="G104" t="inlineStr"/>
     </row>
@@ -3860,17 +3654,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>סוויצאפ</t>
+          <t>אלבה</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>השלמת בדיקות וסיכום לנירה</t>
+          <t>דיון בהשגה במסמ"ק + הכנה</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3878,10 +3672,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
+      <c r="F105" t="n">
+        <v>3.5</v>
       </c>
       <c r="G105" t="inlineStr"/>
     </row>
@@ -3893,17 +3685,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>שיכון עובדים</t>
+          <t>סוויצאפ</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>טיפול בקבלת אישור עיריה</t>
+          <t>השלמת בדיקות וסיכום לנירה</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3911,10 +3703,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="F106" t="n">
+        <v>1.25</v>
       </c>
       <c r="G106" t="inlineStr"/>
     </row>
@@ -3926,17 +3716,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>עתירה מינהלית</t>
+          <t>שיכון עובדים</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>תיקונים לעתירה מתוקנת</t>
+          <t>טיפול בקבלת אישור עיריה</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3944,17 +3734,15 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F107" t="n">
+        <v>0.25</v>
       </c>
       <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>14.02.2026</t>
+          <t>12.02.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3969,7 +3757,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>עתירה מתוקנת ובדיקות</t>
+          <t>תיקונים לעתירה מתוקנת</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3977,32 +3765,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="F108" t="n">
+        <v>2.5</v>
       </c>
       <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>15.02.2026</t>
+          <t>14.02.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>תחנת שורק</t>
+          <t>עתירה מינהלית</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>תיאום פגישה שמאי מחוזי</t>
+          <t>עתירה מתוקנת ובדיקות</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4010,10 +3796,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F109" t="n">
+        <v>1.75</v>
       </c>
       <c r="G109" t="inlineStr"/>
     </row>
@@ -4025,17 +3809,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ש.ב.ה.</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>פרויקט עומר</t>
+          <t>תחנת שורק</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>שיחות בענין מכירת מניות וקרקע</t>
+          <t>תיאום פגישה שמאי מחוזי</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4043,10 +3827,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F110" t="n">
+        <v>0.5</v>
       </c>
       <c r="G110" t="inlineStr"/>
     </row>
@@ -4058,17 +3840,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>גבעוני</t>
+          <t>ש.ב.ה.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>מיסוי מקרקעין</t>
+          <t>פרויקט עומר</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>דיווח למסמ"ק</t>
+          <t>שיחות בענין מכירת מניות וקרקע</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4076,10 +3858,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F111" t="n">
+        <v>0.5</v>
       </c>
       <c r="G111" t="inlineStr"/>
     </row>
@@ -4091,17 +3871,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>בוחבוט</t>
+          <t>גבעוני</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>מעלות</t>
+          <t>מיסוי מקרקעין</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>בקשה לסריקת תיק רמ"י לצורך תיקון השטח</t>
+          <t>דיווח למסמ"ק</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4109,32 +3889,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F112" t="n">
+        <v>0.75</v>
       </c>
       <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>16.02.2026</t>
+          <t>15.02.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>בוחבוט</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>עין יהב</t>
+          <t>מעלות</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>שיחת עדכון פליקס ויהל (כולל דימונה ודלרום)</t>
+          <t>בקשה לסריקת תיק רמ"י לצורך תיקון השטח</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4142,10 +3920,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F113" t="n">
+        <v>0.75</v>
       </c>
       <c r="G113" t="inlineStr"/>
     </row>
@@ -4157,17 +3933,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ש.ב.א</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>תביעה רמ"י</t>
+          <t>עין יהב</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>בדיקת הסכם פשרה לענין ארנונה ושיחה ניצן</t>
+          <t>שיחת עדכון פליקס ויהל (כולל דימונה ודלרום)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4175,10 +3951,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F114" t="n">
+        <v>0.75</v>
       </c>
       <c r="G114" t="inlineStr"/>
     </row>
@@ -4190,17 +3964,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>ש.ב.א</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>עתירה מינהלית</t>
+          <t>תביעה רמ"י</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>תיקונים אחרונים לעתירה מתוקנת והפצת נוסח פנימי</t>
+          <t>בדיקת הסכם פשרה לענין ארנונה ושיחה ניצן</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4208,10 +3982,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F115" t="n">
+        <v>0.5</v>
       </c>
       <c r="G115" t="inlineStr"/>
     </row>
@@ -4223,17 +3995,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>נייר חדרה</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>הסכם מכר או פי סי</t>
+          <t>עתירה מינהלית</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>תיקון טיוטא ביחס לתוספת להסכם שכירות</t>
+          <t>תיקונים אחרונים לעתירה מתוקנת והפצת נוסח פנימי</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4241,10 +4013,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F116" t="n">
+        <v>1.5</v>
       </c>
       <c r="G116" t="inlineStr"/>
     </row>
@@ -4256,17 +4026,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>עודד מרגלית</t>
+          <t>נייר חדרה</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>בית הטקסטיל</t>
+          <t>הסכם מכר או פי סי</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>תיקון טיוטא והפצה</t>
+          <t>תיקון טיוטא ביחס לתוספת להסכם שכירות</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4274,10 +4044,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F117" t="n">
+        <v>1.5</v>
       </c>
       <c r="G117" t="inlineStr"/>
     </row>
@@ -4289,17 +4057,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>גבעוני</t>
+          <t>עודד מרגלית</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>חוות דעת בענין דמי שימוש</t>
+          <t>בית הטקסטיל</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>תיקונים אחרונים והפצת חו"ד חתומה</t>
+          <t>תיקון טיוטא והפצה</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4307,10 +4075,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F118" t="n">
+        <v>2.5</v>
       </c>
       <c r="G118" t="inlineStr"/>
     </row>
@@ -4322,17 +4088,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>גבעוני</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>בית אלבה</t>
+          <t>חוות דעת בענין דמי שימוש</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>מסמכים מוולף למסמ"ק + שיחה אייל ואיציק</t>
+          <t>תיקונים אחרונים והפצת חו"ד חתומה</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4340,10 +4106,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F119" t="n">
+        <v>0.5</v>
       </c>
       <c r="G119" t="inlineStr"/>
     </row>
@@ -4355,17 +4119,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>חלקה 68</t>
+          <t>בית אלבה</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>טיוטת הסכם אופציה והסכם שכירות</t>
+          <t>מסמכים מוולף למסמ"ק + שיחה אייל ואיציק</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4373,32 +4137,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F120" t="n">
+        <v>0.5</v>
       </c>
       <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>18.2.2026</t>
+          <t>16.02.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>נייר חדרה</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>הסכם מכר Opc</t>
+          <t>חלקה 68</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>זום בענין מתוה עסקה</t>
+          <t>טיוטת הסכם אופציה והסכם שכירות</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4406,10 +4168,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F121" t="n">
+        <v>2</v>
       </c>
       <c r="G121" t="inlineStr"/>
     </row>
@@ -4421,17 +4181,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>עודד מרגלית</t>
+          <t>נייר חדרה</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>רכישה בית הטקסטיל</t>
+          <t>הסכם מכר Opc</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>זום בכ מוכרת</t>
+          <t>זום בענין מתוה עסקה</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4439,10 +4199,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F122" t="n">
+        <v>0.75</v>
       </c>
       <c r="G122" t="inlineStr"/>
     </row>
@@ -4454,17 +4212,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>עמרי באואר</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>הדר יוסף</t>
+          <t>עתירה מינהלית</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ישיבת זום</t>
+          <t>הגשת עתירה</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4472,10 +4230,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F123" t="n">
+        <v>0.5</v>
       </c>
       <c r="G123" t="inlineStr"/>
     </row>
@@ -4487,17 +4243,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>שמשון זליג</t>
+          <t>עודד מרגלית</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>הארכת תקופה</t>
+          <t>רכישה בית הטקסטיל</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>רמינלענין קבלת מסמכים מהתיק ומצב חשבון</t>
+          <t>זום בכ מוכרת</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4505,10 +4261,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F124" t="n">
+        <v>1.5</v>
       </c>
       <c r="G124" t="inlineStr"/>
     </row>
@@ -4520,17 +4274,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>אקרשטיין</t>
+          <t>עמרי באואר</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>העברת זכויות</t>
+          <t>הדר יוסף</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>רמי צפון</t>
+          <t>ישיבת זום</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4538,10 +4292,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F125" t="n">
+        <v>1</v>
       </c>
       <c r="G125" t="inlineStr"/>
     </row>
@@ -4553,17 +4305,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>שמשון זליג</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>צליל החורש</t>
+          <t>הארכת תקופה</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>רמי צפון לקבלת היתרים מהתיק</t>
+          <t>רמינלענין קבלת מסמכים מהתיק ומצב חשבון</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4571,10 +4323,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F126" t="n">
+        <v>1</v>
       </c>
       <c r="G126" t="inlineStr"/>
     </row>
@@ -4586,17 +4336,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>גבעוני</t>
+          <t>אקרשטיין</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>הארכת חוזה</t>
+          <t>העברת זכויות</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>רמי מרכז לצורך קבלת חוזה חכירה</t>
+          <t>רמי צפון</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4604,10 +4354,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F127" t="n">
+        <v>1.5</v>
       </c>
       <c r="G127" t="inlineStr"/>
     </row>
@@ -4619,17 +4367,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>בוחבוט</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>מכירת מניות</t>
+          <t>צליל החורש</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>טיפול בדרישת רשות המסים</t>
+          <t>רמי צפון לקבלת היתרים מהתיק</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4637,10 +4385,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F128" t="n">
+        <v>1.5</v>
       </c>
       <c r="G128" t="inlineStr"/>
     </row>
@@ -4652,28 +4398,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>גבעוני</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>אלבה</t>
+          <t>הארכת חוזה</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>טיוטת מייל לרשות המסים בעניין הכרה בהוצאות לרמי</t>
+          <t>רמי מרכז לצורך קבלת חוזה חכירה</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>הוצאות</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1.5</v>
       </c>
       <c r="G129" t="inlineStr"/>
     </row>
@@ -4685,17 +4429,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>מתחם השעון</t>
+          <t>בוחבוט</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>כללי</t>
+          <t>מכירת מניות</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>דוחות כספיים</t>
+          <t>טיפול בדרישת רשות המסים</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4703,10 +4447,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F130" t="n">
+        <v>0.75</v>
       </c>
       <c r="G130" t="inlineStr"/>
     </row>
@@ -4718,50 +4460,48 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>שכירות חניון</t>
+          <t>אלבה</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>תיקון טיוטא</t>
+          <t>טיוטת מייל לרשות המסים בעניין הכרה בהוצאות לרמי</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>גלית</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+          <t>הוצאות</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
       </c>
       <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>18.2.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>אקרשטיין</t>
+          <t>מתחם השעון</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>רישום זכויות</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>התכתבות רמ"י לענין השלמת הרישום</t>
+          <t>דוחות כספיים</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4769,32 +4509,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F132" t="n">
+        <v>0.75</v>
       </c>
       <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>18.2.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>בראבו</t>
+          <t>שכירות חניון</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>הסכם שכירות ושיחה גולן וניר</t>
+          <t>תיקון טיוטא</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4802,10 +4540,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
+      <c r="F133" t="n">
+        <v>1.5</v>
       </c>
       <c r="G133" t="inlineStr"/>
     </row>
@@ -4817,17 +4553,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>אקרשטיין</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>צליל החורש</t>
+          <t>רישום זכויות</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>טיפול מול ליאב בקבלת מסמכי התיק ותשריטים</t>
+          <t>התכתבות רמ"י לענין השלמת הרישום</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4835,10 +4571,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F134" t="n">
+        <v>0.75</v>
       </c>
       <c r="G134" t="inlineStr"/>
     </row>
@@ -4850,17 +4584,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>אודי שגב</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>היטלים</t>
+          <t>בראבו</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>מו"מ דניאל</t>
+          <t>הסכם שכירות ושיחה גולן וניר</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4868,10 +4602,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F135" t="n">
+        <v>1.25</v>
       </c>
       <c r="G135" t="inlineStr"/>
     </row>
@@ -4883,17 +4615,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>אגירה</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>אלקטרה</t>
+          <t>צליל החורש</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>סעיף דילול בהסכם שותפות</t>
+          <t>טיפול מול ליאב בקבלת מסמכי התיק ותשריטים</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4901,10 +4633,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F136" t="n">
+        <v>0.5</v>
       </c>
       <c r="G136" t="inlineStr"/>
     </row>
@@ -4916,17 +4646,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>בוחבוט</t>
+          <t>אודי שגב</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>מעלה מעלות</t>
+          <t>היטלים</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>תבור בדיקות ברשם החברות</t>
+          <t>מו"מ דניאל</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4934,10 +4664,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="F137" t="n">
+        <v>0.75</v>
       </c>
       <c r="G137" t="inlineStr"/>
     </row>
@@ -4949,17 +4677,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>מפעלי נשק</t>
+          <t>אגירה</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>יוניסקופ</t>
+          <t>אלקטרה</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>בדיקת מסמכים קודמים, תיק חברה  והכנת מסמכים להקצאת קרקע</t>
+          <t>סעיף דילול בהסכם שותפות</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4967,10 +4695,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="F138" t="n">
+        <v>1</v>
       </c>
       <c r="G138" t="inlineStr"/>
     </row>
@@ -4982,17 +4708,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>בוחבוט</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>חלקה 68</t>
+          <t>מעלה מעלות</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>תיקונים לטיוטת הסכם אופציה והסכם שכירות</t>
+          <t>תבור בדיקות ברשם החברות</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5000,10 +4726,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="F139" t="n">
+        <v>0.25</v>
       </c>
       <c r="G139" t="inlineStr"/>
     </row>
@@ -5015,17 +4739,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>מפעלי נשק</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>רכישה אלבה</t>
+          <t>יוניסקופ</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>שיחה מעיין מסמ"ק ומסמכים נוספים לענין מס שבח</t>
+          <t>בדיקת מסמכים קודמים, תיק חברה  והכנת מסמכים להקצאת קרקע</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5033,10 +4757,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F140" t="n">
+        <v>4.5</v>
       </c>
       <c r="G140" t="inlineStr"/>
     </row>
@@ -5048,17 +4770,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>כפיר דהן</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>קצרין</t>
+          <t>חלקה 68</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>מסמכים לרישום זכויות</t>
+          <t>תיקונים לטיוטת הסכם אופציה והסכם שכירות</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5066,32 +4788,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F141" t="n">
+        <v>0.25</v>
       </c>
       <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>20.02.2026</t>
+          <t>19.02.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>אודי שגב</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>היטלים</t>
+          <t>רכישה אלבה</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>בדיקת פשרה מוצעת והתכתבות רוית</t>
+          <t>שיחה מעיין מסמ"ק ומסמכים נוספים לענין מס שבח</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5099,32 +4819,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F142" t="n">
+        <v>1.5</v>
       </c>
       <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>21.02.2026</t>
+          <t>19.02.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>נייר חדרה</t>
+          <t>כפיר דהן</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>חלקה 26</t>
+          <t>קצרין</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>מכתב תזכורת לרמ"י להארכת חוזה</t>
+          <t>מסמכים לרישום זכויות</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5132,32 +4850,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F143" t="n">
+        <v>0.5</v>
       </c>
       <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>20.02.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>אודי שגב</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>מבשרת ציון</t>
+          <t>היטלים</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>פגישה עם יעל במשרד + נקודות לתביעה למפקח</t>
+          <t>בדיקת פשרה מוצעת והתכתבות רוית</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5165,32 +4881,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F144" t="n">
+        <v>0.5</v>
       </c>
       <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>21.02.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>אגירה</t>
+          <t>נייר חדרה</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>אלקטרה</t>
+          <t>חלקה 26</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>שיחה אלקטרה לענין סעיף דילול בהסכם שותפות</t>
+          <t>מכתב תזכורת לרמ"י להארכת חוזה</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5198,10 +4912,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F145" t="n">
+        <v>0.75</v>
       </c>
       <c r="G145" t="inlineStr"/>
     </row>
@@ -5213,17 +4925,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>בוחבוט</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>חובבי ציון</t>
+          <t>מבשרת ציון</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>שיחת ועידה לענין רישום הבית המשותף ובדיקות מקדימות ומסמכי פירוק</t>
+          <t>פגישה עם יעל במשרד + נקודות לתביעה למפקח</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5231,10 +4943,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F146" t="n">
+        <v>2.5</v>
       </c>
       <c r="G146" t="inlineStr"/>
     </row>
@@ -5246,17 +4956,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>אסתי וייץ</t>
+          <t>אגירה</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>גלגלי הפלדה</t>
+          <t>אלקטרה</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>רמ"י מרכז (רחלה) לענין הקניית הבעלות וקידום שמאות</t>
+          <t>שיחה אלקטרה לענין סעיף דילול בהסכם שותפות</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5264,10 +4974,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F147" t="n">
+        <v>1</v>
       </c>
       <c r="G147" t="inlineStr"/>
     </row>
@@ -5279,17 +4987,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>בוחבוט</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>עתירה מינהלית</t>
+          <t>חובבי ציון</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>טיוטת תגובה לבקשת ההצטרפות</t>
+          <t>שיחת ועידה לענין רישום הבית המשותף ובדיקות מקדימות ומסמכי פירוק</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5297,10 +5005,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F148" t="n">
+        <v>2</v>
       </c>
       <c r="G148" t="inlineStr"/>
     </row>
@@ -5312,17 +5018,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>מלכה רובין</t>
+          <t>אסתי וייץ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>נשר</t>
+          <t>גלגלי הפלדה</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>מסמכים להקניית הבעלות</t>
+          <t>רמ"י מרכז (רחלה) לענין הקניית הבעלות וקידום שמאות</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5330,10 +5036,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F149" t="n">
+        <v>1.5</v>
       </c>
       <c r="G149" t="inlineStr"/>
     </row>
@@ -5345,17 +5049,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>אגרוטופ</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>תימורים</t>
+          <t>עתירה מינהלית</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>עדכון למנהלים המיוחדים</t>
+          <t>טיוטת תגובה לבקשת ההצטרפות</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5363,10 +5067,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F150" t="n">
+        <v>2.5</v>
       </c>
       <c r="G150" t="inlineStr"/>
     </row>
@@ -5378,17 +5080,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>מלכה רובין</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>חלקה 68</t>
+          <t>נשר</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>בדיקת ייעודי קרקע + שיחה רלי</t>
+          <t>מסמכים להקניית הבעלות</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5396,10 +5098,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F151" t="n">
+        <v>1</v>
       </c>
       <c r="G151" t="inlineStr"/>
     </row>
@@ -5411,17 +5111,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>מפעלי נשק</t>
+          <t>אגרוטופ</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>יוניסקופ</t>
+          <t>תימורים</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>השלמת  מסמכים להקצאת קרקע</t>
+          <t>עדכון למנהלים המיוחדים</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5429,10 +5129,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F152" t="n">
+        <v>1.5</v>
       </c>
       <c r="G152" t="inlineStr"/>
     </row>
@@ -5444,17 +5142,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>עין יהב</t>
+          <t>חלקה 68</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>בדיקת מסמכי חברה תאגיד ועסקאות קודמות</t>
+          <t>בדיקת ייעודי קרקע + שיחה רלי</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5462,17 +5160,15 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F153" t="n">
+        <v>1</v>
       </c>
       <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5487,7 +5183,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>מרחב צפון רמ"י לקידום הקצאת הקרקע</t>
+          <t>השלמת  מסמכים להקצאת קרקע</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5495,17 +5191,15 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="F154" t="n">
+        <v>2.5</v>
       </c>
       <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5515,12 +5209,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>צליל החורש</t>
+          <t>עין יהב</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>מרחב צפון פגישה ליאב לצורך קבלת הליך קודם ושיחה אסף</t>
+          <t>בדיקת מסמכי חברה תאגיד ועסקאות קודמות</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5528,10 +5222,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F155" t="n">
+        <v>1.5</v>
       </c>
       <c r="G155" t="inlineStr"/>
     </row>
@@ -5543,17 +5235,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>כפיר דהן</t>
+          <t>מפעלי נשק</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>כדורי</t>
+          <t>יוניסקופ</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>מרחב צפון לענין רישומים</t>
+          <t>מרחב צפון רמ"י לקידום הקצאת הקרקע</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5561,10 +5253,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F156" t="n">
+        <v>4.5</v>
       </c>
       <c r="G156" t="inlineStr"/>
     </row>
@@ -5576,17 +5266,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>אקרשטיין</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>רישום זכויות</t>
+          <t>צליל החורש</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>מרחב צפון (חלי) להשלמת העברת הזכויות</t>
+          <t>מרחב צפון פגישה ליאב לצורך קבלת הליך קודם ושיחה אסף</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5594,10 +5284,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F157" t="n">
+        <v>1</v>
       </c>
       <c r="G157" t="inlineStr"/>
     </row>
@@ -5609,17 +5297,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>כפיר דהן</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>קרית שמונה</t>
+          <t>כדורי</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>פגישה מרחב צפון חלי + ליאב לתיקון שטח החוזה</t>
+          <t>מרחב צפון לענין רישומים</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5627,10 +5315,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F158" t="n">
+        <v>0.5</v>
       </c>
       <c r="G158" t="inlineStr"/>
     </row>
@@ -5642,17 +5328,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>גורדון 37</t>
+          <t>אקרשטיין</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>פינוי בינוי</t>
+          <t>רישום זכויות</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>פגישת זום וטיוטת מכתב לרה"ע</t>
+          <t>מרחב צפון (חלי) להשלמת העברת הזכויות</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5660,10 +5346,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F159" t="n">
+        <v>1</v>
       </c>
       <c r="G159" t="inlineStr"/>
     </row>
@@ -5675,17 +5359,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ש.ב.ה.</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>פרויקט עומר</t>
+          <t>קרית שמונה</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>שיחות בענין מכירת מניות וקרקע</t>
+          <t>פגישה מרחב צפון חלי + ליאב לתיקון שטח החוזה</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5693,10 +5377,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F160" t="n">
+        <v>2.5</v>
       </c>
       <c r="G160" t="inlineStr"/>
     </row>
@@ -5708,17 +5390,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>גורדון 37</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>מבשרת ציון</t>
+          <t>פינוי בינוי</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>בדיקת שטחים בהיתרי בניה קודמים</t>
+          <t>פגישת זום וטיוטת מכתב לרה"ע</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5726,10 +5408,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F161" t="n">
+        <v>1.5</v>
       </c>
       <c r="G161" t="inlineStr"/>
     </row>
@@ -5746,12 +5426,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>חברת נוסטרו</t>
+          <t>פרויקט עומר</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>טיוטת הסכם לייסוד חברה</t>
+          <t>שיחות בענין מכירת מניות וקרקע</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5759,10 +5439,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F162" t="n">
+        <v>1.5</v>
       </c>
       <c r="G162" t="inlineStr"/>
     </row>
@@ -5774,17 +5452,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ש.ב.א</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>תביעה רמ"י</t>
+          <t>מבשרת ציון</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>השלמת חוות דעת - תיקונים למודד</t>
+          <t>בדיקת שטחים בהיתרי בניה קודמים</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -5792,32 +5470,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F163" t="n">
+        <v>0.75</v>
       </c>
       <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>מלכה רובין</t>
+          <t>ש.ב.ה.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>נשר</t>
+          <t>חברת נוסטרו</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>פגישה במשרד</t>
+          <t>טיוטת הסכם לייסוד חברה</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5825,32 +5501,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F164" t="n">
+        <v>1.5</v>
       </c>
       <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>אודי שגב</t>
+          <t>ש.ב.א</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>היטלים</t>
+          <t>תביעה רמ"י</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>שיחה רוית לענין הצעה דניאל</t>
+          <t>השלמת חוות דעת - תיקונים למודד</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5858,10 +5532,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F165" t="n">
+        <v>0.75</v>
       </c>
       <c r="G165" t="inlineStr"/>
     </row>
@@ -5873,17 +5545,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ש.ב.א</t>
+          <t>מלכה רובין</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>תביעה רמ"י</t>
+          <t>נשר</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>השלמת חוות דעת ושיחה אברבוך - תיקונים למודד</t>
+          <t>פגישה במשרד</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -5891,10 +5563,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F166" t="n">
+        <v>0.75</v>
       </c>
       <c r="G166" t="inlineStr"/>
     </row>
@@ -5906,17 +5576,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>אודי שגב</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>מבשרת ציון</t>
+          <t>היטלים</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>בדיקות משפטיות</t>
+          <t>שיחה רוית לענין הצעה דניאל</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5924,10 +5594,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F167" t="n">
+        <v>1</v>
       </c>
       <c r="G167" t="inlineStr"/>
     </row>
@@ -5939,17 +5607,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>ש.ב.א</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>חניון רוטשילד</t>
+          <t>תביעה רמ"י</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>תיקונים לטיוטא</t>
+          <t>השלמת חוות דעת ושיחה אברבוך - תיקונים למודד</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5957,10 +5625,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F168" t="n">
+        <v>0.75</v>
       </c>
       <c r="G168" t="inlineStr"/>
     </row>
@@ -5972,17 +5638,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>תחנת שורק</t>
+          <t>מבשרת ציון</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>קריאת החלטת שמאית מחוזית + שיחה דרור</t>
+          <t>בדיקות משפטיות</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5990,10 +5656,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F169" t="n">
+        <v>2.5</v>
       </c>
       <c r="G169" t="inlineStr"/>
     </row>
@@ -6005,17 +5669,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>גבעוני</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>הארכת חכירה</t>
+          <t>חניון רוטשילד</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>שוטף מול דפנה</t>
+          <t>תיקונים לטיוטא</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6023,10 +5687,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="F170" t="n">
+        <v>1</v>
       </c>
       <c r="G170" t="inlineStr"/>
     </row>
@@ -6038,17 +5700,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>חלקה 68</t>
+          <t>תחנת שורק</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>תיקונים לטיוטא ושיחה יאיר</t>
+          <t>קריאת החלטת שמאית מחוזית + שיחה דרור</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6056,10 +5718,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F171" t="n">
+        <v>1.5</v>
       </c>
       <c r="G171" t="inlineStr"/>
     </row>
@@ -6071,17 +5731,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>עקיבא איגר</t>
+          <t>גבעוני</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>רוכשים</t>
+          <t>הארכת חכירה</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>טיפול ברישום ה"א</t>
+          <t>שוטף מול דפנה</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -6089,10 +5749,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F172" t="n">
+        <v>0.25</v>
       </c>
       <c r="G172" t="inlineStr"/>
     </row>
@@ -6104,17 +5762,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ינושבסקי</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>אבן גבירול</t>
+          <t>חלקה 68</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>טיפול במשכנתאות</t>
+          <t>תיקונים לטיוטא ושיחה יאיר</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6122,10 +5780,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F173" t="n">
+        <v>0.75</v>
       </c>
       <c r="G173" t="inlineStr"/>
     </row>
@@ -6137,17 +5793,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>נייר חדרה</t>
+          <t>עקיבא איגר</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>חלקה 70</t>
+          <t>רוכשים</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>מסמכים לרישום פרצלציה</t>
+          <t>טיפול ברישום ה"א</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6155,32 +5811,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F174" t="n">
+        <v>1</v>
       </c>
       <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>25.2.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>ינושבסקי</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>צליל החורש</t>
+          <t>אבן גבירול</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ביקור במרחב צפון לקבלת תשריטים נוספים ומסמכי תביעה</t>
+          <t>טיפול במשכנתאות</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6188,32 +5842,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F175" t="n">
+        <v>0.75</v>
       </c>
       <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>25.2.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>נייר חדרה</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>קרית שמונה</t>
+          <t>חלקה 70</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>מרחב צפון לצורך תיקון שטח חוזה</t>
+          <t>מסמכים לרישום פרצלציה</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6221,10 +5873,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F176" t="n">
+        <v>0.75</v>
       </c>
       <c r="G176" t="inlineStr"/>
     </row>
@@ -6236,17 +5886,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>יוני סקופ</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>הקצאת קרקע</t>
+          <t>צליל החורש</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ביקור במרחב צפון לקידום הבקשה</t>
+          <t>ביקור במרחב צפון לקבלת תשריטים נוספים ומסמכי תביעה</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6254,10 +5904,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="F177" t="n">
+        <v>2</v>
       </c>
       <c r="G177" t="inlineStr"/>
     </row>
@@ -6269,17 +5917,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>אקרשטיין</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>העברת זכויות</t>
+          <t>קרית שמונה</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>מרחב צפון לקידום התיק</t>
+          <t>מרחב צפון לצורך תיקון שטח חוזה</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6287,10 +5935,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F178" t="n">
+        <v>2.5</v>
       </c>
       <c r="G178" t="inlineStr"/>
     </row>
@@ -6302,17 +5948,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>יוני סקופ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>תביעה למפקח</t>
+          <t>הקצאת קרקע</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>תיקונים לכתב תביעה + שיחת ועידה ענת ויעל</t>
+          <t>ביקור במרחב צפון לקידום הבקשה</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6320,32 +5966,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F179" t="n">
+        <v>4.5</v>
       </c>
       <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>25.2.2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>אקרשטיין</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>צליל החורש</t>
+          <t>העברת זכויות</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>שוטף</t>
+          <t>מרחב צפון לקידום התיק</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6353,32 +5997,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F180" t="n">
+        <v>1.5</v>
       </c>
       <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>25.2.2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>כפיר דהן</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>כדורי</t>
+          <t>תביעה למפקח</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>מכירת קרקע - טיפול בהשלמת עסקה קודמת</t>
+          <t>תיקונים לכתב תביעה + שיחת ועידה ענת ויעל</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6386,10 +6028,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F181" t="n">
+        <v>2.5</v>
       </c>
       <c r="G181" t="inlineStr"/>
     </row>
@@ -6401,17 +6041,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>משרד</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>כללי</t>
+          <t>צליל החורש</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>דב הלפרן - בדיקת מסמכים והצעת שכ"ט</t>
+          <t>שוטף</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6419,10 +6059,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F182" t="n">
+        <v>0.5</v>
       </c>
       <c r="G182" t="inlineStr"/>
     </row>
@@ -6434,17 +6072,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>כפיר דהן</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>מבקשת ציון</t>
+          <t>כדורי</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>כתב תביעה למפקחת תיקונים אחרונים והגשה</t>
+          <t>מכירת קרקע - טיפול בהשלמת עסקה קודמת</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6452,10 +6090,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F183" t="n">
+        <v>0.75</v>
       </c>
       <c r="G183" t="inlineStr"/>
     </row>
@@ -6467,17 +6103,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>מפעלי נשק</t>
+          <t>משרד</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>יוניסקופ</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>צירוף מדידות לרמ"י לעדכון הבקשה</t>
+          <t>דב הלפרן - בדיקת מסמכים והצעת שכ"ט</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6485,10 +6121,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F184" t="n">
+        <v>1</v>
       </c>
       <c r="G184" t="inlineStr"/>
     </row>
@@ -6500,17 +6134,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>כפיר דהן</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>מכירת נכס</t>
+          <t>מבקשת ציון</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>תיקונים להסכם מכר כדורי + שיחות כפיר</t>
+          <t>כתב תביעה למפקחת תיקונים אחרונים והגשה</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6518,10 +6152,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F185" t="n">
+        <v>3</v>
       </c>
       <c r="G185" t="inlineStr"/>
     </row>
@@ -6533,17 +6165,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>מפעלי נשק</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>אלבה</t>
+          <t>יוניסקופ</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>מסמ"ק אישורים העברה</t>
+          <t>צירוף מדידות לרמ"י לעדכון הבקשה</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6551,10 +6183,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F186" t="n">
+        <v>0.5</v>
       </c>
       <c r="G186" t="inlineStr"/>
     </row>
@@ -6571,12 +6201,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>קצרין</t>
+          <t>מכירת נכס</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>השלמת עסקה ומסמכי בנק</t>
+          <t>תיקונים להסכם מכר כדורי + שיחות כפיר</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6584,32 +6214,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F187" t="n">
+        <v>2</v>
       </c>
       <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>27.02.2026</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ש.ב.א</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>תביעה רמ"י</t>
+          <t>אלבה</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>תיקונים ובדיקות לחוות דעת מומחה (מודד)</t>
+          <t>מסמ"ק אישורים העברה</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6617,32 +6245,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F188" t="n">
+        <v>0.75</v>
       </c>
       <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>27.02.2026</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ירדן חובב</t>
+          <t>כפיר דהן</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>רכישת דירה</t>
+          <t>קצרין</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>התייחסות להסכם מכר</t>
+          <t>השלמת עסקה ומסמכי בנק</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6650,32 +6276,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F189" t="n">
+        <v>1</v>
       </c>
       <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>27.02.2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>ש.ב.א</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>נחשון</t>
+          <t>תביעה רמ"י</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>טיפול בהעברת זכויות, שיחות חני, מסמכים לרמי</t>
+          <t>תיקונים ובדיקות לחוות דעת מומחה (מודד)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6683,32 +6307,30 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F190" t="n">
+        <v>1.5</v>
       </c>
       <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>27.02.2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>ירדן חובב</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>צליל החורש</t>
+          <t>רכישת דירה</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>תיקון והקניית בעלות-שיחה אסף, בדיקת תשריטים, בדיקת היתרי בניה ותיק בניין בוועדה</t>
+          <t>התייחסות להסכם מכר</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -6716,10 +6338,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F191" t="n">
+        <v>1</v>
       </c>
       <c r="G191" t="inlineStr"/>
     </row>
@@ -6731,17 +6351,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>עתירה מינהלית</t>
+          <t>נחשון</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>תגובה לבקשת הצטרפות רוכשות</t>
+          <t>טיפול בהעברת זכויות, שיחות חני, מסמכים לרמי</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6749,10 +6369,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F192" t="n">
+        <v>1.5</v>
       </c>
       <c r="G192" t="inlineStr"/>
     </row>
@@ -6764,17 +6382,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>עתירה מינהלית</t>
+          <t>צליל החורש</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>עתירה מתוקנת</t>
+          <t>תיקון והקניית בעלות-שיחה אסף, בדיקת תשריטים, בדיקת היתרי בניה ותיק בניין בוועדה</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6782,10 +6400,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
+      <c r="F193" t="n">
+        <v>1.5</v>
       </c>
       <c r="G193" t="inlineStr"/>
     </row>
@@ -6802,12 +6418,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>הר בלאן</t>
+          <t>עתירה מינהלית</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>מכתב התראה לרוכשות</t>
+          <t>תגובה לבקשת הצטרפות רוכשות</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -6815,10 +6431,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="F194" t="n">
+        <v>2.5</v>
       </c>
       <c r="G194" t="inlineStr"/>
     </row>
@@ -6830,17 +6444,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>עודד מרגלית</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>רכישה בית הטקסטיל</t>
+          <t>עתירה מינהלית</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>תיקון טיוטה ושיחה נווה</t>
+          <t>עתירה מתוקנת</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -6848,10 +6462,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F195" t="n">
+        <v>2.5</v>
       </c>
       <c r="G195" t="inlineStr"/>
     </row>
@@ -6863,17 +6475,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>בראבו</t>
+          <t>הר בלאן</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>שיחת Zoom תיקון הסכם שכירות</t>
+          <t>מכתב התראה לרוכשות</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -6881,10 +6493,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="F196" t="n">
+        <v>1.75</v>
       </c>
       <c r="G196" t="inlineStr"/>
     </row>
@@ -6896,17 +6506,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>עודד מרגלית</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>מבשרת ציון</t>
+          <t>רכישה בית הטקסטיל</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>שיחת ועידה בעניין הגשת ערר</t>
+          <t>תיקון טיוטה ושיחה נווה</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -6914,10 +6524,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>0.75.</t>
-        </is>
+      <c r="F197" t="n">
+        <v>2</v>
       </c>
       <c r="G197" t="inlineStr"/>
     </row>
@@ -6929,17 +6537,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>אגירה</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>בנק לאומי</t>
+          <t>בראבו</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>שיחת Zoom בעניין מתווה לאשראי</t>
+          <t>שיחת Zoom תיקון הסכם שכירות</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -6947,10 +6555,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="F198" t="n">
+        <v>0.75</v>
       </c>
       <c r="G198" t="inlineStr"/>
     </row>
@@ -6962,17 +6568,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>שמשון זליג</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>הארכה תקופה</t>
+          <t>מבשרת ציון</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ישיבה פנימית</t>
+          <t>שיחת ועידה בעניין הגשת ערר</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -6980,10 +6586,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F199" t="n">
+        <v>0.75</v>
       </c>
       <c r="G199" t="inlineStr"/>
     </row>
@@ -6995,17 +6599,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>סיגת</t>
+          <t>אגירה</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>הארכת תקופה</t>
+          <t>בנק לאומי</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ישיבה פנימית בדיקת מדידות ומכתב לרמי</t>
+          <t>שיחת Zoom בעניין מתווה לאשראי</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -7013,10 +6617,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F200" t="n">
+        <v>0.5</v>
       </c>
       <c r="G200" t="inlineStr"/>
     </row>
@@ -7028,17 +6630,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>שמשון זליג</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>אופקים</t>
+          <t>הארכה תקופה</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>שיחה לירון זה העברת מסמכים בעניין הארכת תקופת חכירה חוזה שמעון אטיאס</t>
+          <t>ישיבה פנימית</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -7046,10 +6648,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F201" t="n">
+        <v>1.5</v>
       </c>
       <c r="G201" t="inlineStr"/>
     </row>
@@ -7061,17 +6661,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>נייר חדרה</t>
+          <t>סיגת</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>הסכם מכרOPC</t>
+          <t>הארכת תקופה</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ישיבה פנימית</t>
+          <t>ישיבה פנימית בדיקת מדידות ומכתב לרמי</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -7079,10 +6679,8 @@
           <t>גלית</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="F202" t="n">
+        <v>1.5</v>
       </c>
       <c r="G202" t="inlineStr"/>
     </row>
@@ -7094,30 +6692,90 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
+          <t>דלק</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>אופקים</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>שיחה לירון זה העברת מסמכים בעניין הארכת תקופת חכירה חוזה שמעון אטיאס</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>17.2.2036</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>נייר חדרה</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>הסכם מכרOPC</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ישיבה פנימית</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>17.2.2036</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
           <t>עקיבא איגר</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>רוכשים</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>טיפול במסירת דירה 6</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>גלית</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G205" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/hours_02-2026.xlsx
+++ b/reports/hours_02-2026.xlsx
@@ -1324,7 +1324,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2.2.2026</t>
+          <t>02.02.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4176,22 +4176,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>18.2.2026</t>
+          <t>17.2.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>נייר חדרה</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>הסכם מכר Opc</t>
+          <t>נחשון</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>זום בענין מתוה עסקה</t>
+          <t>טיפול בהעברת זכויות, שיחות חני, מסמכים לרמי</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4200,29 +4200,29 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>18.2.2026</t>
+          <t>17.2.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>עתירה מינהלית</t>
+          <t>צליל החורש</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>הגשת עתירה</t>
+          <t>תיקון והקניית בעלות-שיחה אסף, בדיקת תשריטים, בדיקת היתרי בניה ותיק בניין בוועדה</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4231,29 +4231,29 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>18.2.2026</t>
+          <t>17.2.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>עודד מרגלית</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>רכישה בית הטקסטיל</t>
+          <t>עתירה מינהלית</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>זום בכ מוכרת</t>
+          <t>תגובה לבקשת הצטרפות רוכשות</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4262,29 +4262,29 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>18.2.2026</t>
+          <t>17.2.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>עמרי באואר</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>הדר יוסף</t>
+          <t>עתירה מינהלית</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ישיבת זום</t>
+          <t>עתירה מתוקנת</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4293,29 +4293,29 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>18.2.2026</t>
+          <t>17.2.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>שמשון זליג</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>הארכת תקופה</t>
+          <t>הר בלאן</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>רמינלענין קבלת מסמכים מהתיק ומצב חשבון</t>
+          <t>מכתב התראה לרוכשות</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4324,29 +4324,29 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>18.2.2026</t>
+          <t>17.2.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>אקרשטיין</t>
+          <t>עודד מרגלית</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>העברת זכויות</t>
+          <t>רכישה בית הטקסטיל</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>רמי צפון</t>
+          <t>תיקון טיוטה ושיחה נווה</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4355,29 +4355,29 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>18.2.2026</t>
+          <t>17.2.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>צליל החורש</t>
+          <t>בראבו</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>רמי צפון לקבלת היתרים מהתיק</t>
+          <t>שיחת Zoom תיקון הסכם שכירות</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4386,29 +4386,29 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>18.2.2026</t>
+          <t>17.2.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>גבעוני</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>הארכת חוזה</t>
+          <t>מבשרת ציון</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>רמי מרכז לצורך קבלת חוזה חכירה</t>
+          <t>שיחת ועידה בעניין הגשת ערר</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4417,29 +4417,29 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>18.2.2026</t>
+          <t>17.2.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>בוחבוט</t>
+          <t>אגירה</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>מכירת מניות</t>
+          <t>בנק לאומי</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>טיפול בדרישת רשות המסים</t>
+          <t>שיחת Zoom בעניין מתווה לאשראי</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4448,60 +4448,60 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>18.2.2026</t>
+          <t>17.2.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>שמשון זליג</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>אלבה</t>
+          <t>הארכה תקופה</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>טיוטת מייל לרשות המסים בעניין הכרה בהוצאות לרמי</t>
+          <t>ישיבה פנימית</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>הוצאות</t>
+          <t>גלית</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>18.2.2026</t>
+          <t>17.2.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>מתחם השעון</t>
+          <t>סיגת</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>כללי</t>
+          <t>הארכת תקופה</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>דוחות כספיים</t>
+          <t>ישיבה פנימית בדיקת מדידות ומכתב לרמי</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4510,29 +4510,29 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>18.2.2026</t>
+          <t>17.2.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>שכירות חניון</t>
+          <t>אופקים</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>תיקון טיוטא</t>
+          <t>שיחה לירון זה העברת מסמכים בעניין הארכת תקופת חכירה חוזה שמעון אטיאס</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4548,22 +4548,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>17.2.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>אקרשטיין</t>
+          <t>נייר חדרה</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>רישום זכויות</t>
+          <t>הסכם מכרOPC</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>התכתבות רמ"י לענין השלמת הרישום</t>
+          <t>ישיבה פנימית</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4572,29 +4572,29 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>17.2.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>עקיבא איגר</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>בראבו</t>
+          <t>רוכשים</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>הסכם שכירות ושיחה גולן וניר</t>
+          <t>טיפול במסירת דירה 6</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4603,29 +4603,29 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>18.2.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>נייר חדרה</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>צליל החורש</t>
+          <t>הסכם מכר Opc</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>טיפול מול ליאב בקבלת מסמכי התיק ותשריטים</t>
+          <t>זום בענין מתוה עסקה</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4634,29 +4634,29 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>18.2.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>אודי שגב</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>היטלים</t>
+          <t>עתירה מינהלית</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>מו"מ דניאל</t>
+          <t>הגשת עתירה</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4665,29 +4665,29 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>18.2.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>אגירה</t>
+          <t>עודד מרגלית</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>אלקטרה</t>
+          <t>רכישה בית הטקסטיל</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>סעיף דילול בהסכם שותפות</t>
+          <t>זום בכ מוכרת</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4696,29 +4696,29 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>18.2.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>בוחבוט</t>
+          <t>עמרי באואר</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>מעלה מעלות</t>
+          <t>הדר יוסף</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>תבור בדיקות ברשם החברות</t>
+          <t>ישיבת זום</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4727,29 +4727,29 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>18.2.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>מפעלי נשק</t>
+          <t>שמשון זליג</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>יוניסקופ</t>
+          <t>הארכת תקופה</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>בדיקת מסמכים קודמים, תיק חברה  והכנת מסמכים להקצאת קרקע</t>
+          <t>רמינלענין קבלת מסמכים מהתיק ומצב חשבון</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4758,29 +4758,29 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>18.2.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>אקרשטיין</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>חלקה 68</t>
+          <t>העברת זכויות</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>תיקונים לטיוטת הסכם אופציה והסכם שכירות</t>
+          <t>רמי צפון</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4789,29 +4789,29 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>18.2.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>רכישה אלבה</t>
+          <t>צליל החורש</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>שיחה מעיין מסמ"ק ומסמכים נוספים לענין מס שבח</t>
+          <t>רמי צפון לקבלת היתרים מהתיק</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4827,22 +4827,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>18.2.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>כפיר דהן</t>
+          <t>גבעוני</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>קצרין</t>
+          <t>הארכת חוזה</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>מסמכים לרישום זכויות</t>
+          <t>רמי מרכז לצורך קבלת חוזה חכירה</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4851,29 +4851,29 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>20.02.2026</t>
+          <t>18.2.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>אודי שגב</t>
+          <t>בוחבוט</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>היטלים</t>
+          <t>מכירת מניות</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>בדיקת פשרה מוצעת והתכתבות רוית</t>
+          <t>טיפול בדרישת רשות המסים</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4882,60 +4882,60 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>21.02.2026</t>
+          <t>18.2.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>נייר חדרה</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>חלקה 26</t>
+          <t>אלבה</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>מכתב תזכורת לרמ"י להארכת חוזה</t>
+          <t>טיוטת מייל לרשות המסים בעניין הכרה בהוצאות לרמי</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>גלית</t>
+          <t>הוצאות</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>18.2.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>מתחם השעון</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>מבשרת ציון</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>פגישה עם יעל במשרד + נקודות לתביעה למפקח</t>
+          <t>דוחות כספיים</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4944,29 +4944,29 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>18.2.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>אגירה</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>אלקטרה</t>
+          <t>שכירות חניון</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>שיחה אלקטרה לענין סעיף דילול בהסכם שותפות</t>
+          <t>תיקון טיוטא</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4975,29 +4975,29 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>19.02.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>בוחבוט</t>
+          <t>אקרשטיין</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>חובבי ציון</t>
+          <t>רישום זכויות</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>שיחת ועידה לענין רישום הבית המשותף ובדיקות מקדימות ומסמכי פירוק</t>
+          <t>התכתבות רמ"י לענין השלמת הרישום</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5006,29 +5006,29 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>19.02.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>אסתי וייץ</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>גלגלי הפלדה</t>
+          <t>בראבו</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>רמ"י מרכז (רחלה) לענין הקניית הבעלות וקידום שמאות</t>
+          <t>הסכם שכירות ושיחה גולן וניר</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5037,29 +5037,29 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>19.02.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>עתירה מינהלית</t>
+          <t>צליל החורש</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>טיוטת תגובה לבקשת ההצטרפות</t>
+          <t>טיפול מול ליאב בקבלת מסמכי התיק ותשריטים</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5068,29 +5068,29 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>19.02.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>מלכה רובין</t>
+          <t>אודי שגב</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>נשר</t>
+          <t>היטלים</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>מסמכים להקניית הבעלות</t>
+          <t>מו"מ דניאל</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5099,29 +5099,29 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>19.02.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>אגרוטופ</t>
+          <t>אגירה</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>תימורים</t>
+          <t>אלקטרה</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>עדכון למנהלים המיוחדים</t>
+          <t>סעיף דילול בהסכם שותפות</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5130,29 +5130,29 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>19.02.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>בוחבוט</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>חלקה 68</t>
+          <t>מעלה מעלות</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>בדיקת ייעודי קרקע + שיחה רלי</t>
+          <t>תבור בדיקות ברשם החברות</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5161,14 +5161,14 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>19.02.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>השלמת  מסמכים להקצאת קרקע</t>
+          <t>בדיקת מסמכים קודמים, תיק חברה  והכנת מסמכים להקצאת קרקע</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5192,29 +5192,29 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>19.02.2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>עין יהב</t>
+          <t>חלקה 68</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>בדיקת מסמכי חברה תאגיד ועסקאות קודמות</t>
+          <t>תיקונים לטיוטת הסכם אופציה והסכם שכירות</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5223,29 +5223,29 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>19.02.2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>מפעלי נשק</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>יוניסקופ</t>
+          <t>רכישה אלבה</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>מרחב צפון רמ"י לקידום הקצאת הקרקע</t>
+          <t>שיחה מעיין מסמ"ק ומסמכים נוספים לענין מס שבח</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5254,29 +5254,29 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>19.02.2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>כפיר דהן</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>צליל החורש</t>
+          <t>קצרין</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>מרחב צפון פגישה ליאב לצורך קבלת הליך קודם ושיחה אסף</t>
+          <t>מסמכים לרישום זכויות</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5285,29 +5285,29 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>20.02.2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>כפיר דהן</t>
+          <t>אודי שגב</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>כדורי</t>
+          <t>היטלים</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>מרחב צפון לענין רישומים</t>
+          <t>בדיקת פשרה מוצעת והתכתבות רוית</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5323,22 +5323,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>21.02.2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>אקרשטיין</t>
+          <t>נייר חדרה</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>רישום זכויות</t>
+          <t>חלקה 26</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>מרחב צפון (חלי) להשלמת העברת הזכויות</t>
+          <t>מכתב תזכורת לרמ"י להארכת חוזה</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5347,29 +5347,29 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>קרית שמונה</t>
+          <t>מבשרת ציון</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>פגישה מרחב צפון חלי + ליאב לתיקון שטח החוזה</t>
+          <t>פגישה עם יעל במשרד + נקודות לתביעה למפקח</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5385,22 +5385,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>גורדון 37</t>
+          <t>אגירה</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>פינוי בינוי</t>
+          <t>אלקטרה</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>פגישת זום וטיוטת מכתב לרה"ע</t>
+          <t>שיחה אלקטרה לענין סעיף דילול בהסכם שותפות</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5409,29 +5409,29 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ש.ב.ה.</t>
+          <t>בוחבוט</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>פרויקט עומר</t>
+          <t>חובבי ציון</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>שיחות בענין מכירת מניות וקרקע</t>
+          <t>שיחת ועידה לענין רישום הבית המשותף ובדיקות מקדימות ומסמכי פירוק</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5440,29 +5440,29 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>אסתי וייץ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>מבשרת ציון</t>
+          <t>גלגלי הפלדה</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>בדיקת שטחים בהיתרי בניה קודמים</t>
+          <t>רמ"י מרכז (רחלה) לענין הקניית הבעלות וקידום שמאות</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -5471,29 +5471,29 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ש.ב.ה.</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>חברת נוסטרו</t>
+          <t>עתירה מינהלית</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>טיוטת הסכם לייסוד חברה</t>
+          <t>טיוטת תגובה לבקשת ההצטרפות</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5502,29 +5502,29 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ש.ב.א</t>
+          <t>מלכה רובין</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>תביעה רמ"י</t>
+          <t>נשר</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>השלמת חוות דעת - תיקונים למודד</t>
+          <t>מסמכים להקניית הבעלות</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5533,29 +5533,29 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>מלכה רובין</t>
+          <t>אגרוטופ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>נשר</t>
+          <t>תימורים</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>פגישה במשרד</t>
+          <t>עדכון למנהלים המיוחדים</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -5564,29 +5564,29 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>אודי שגב</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>היטלים</t>
+          <t>חלקה 68</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>שיחה רוית לענין הצעה דניאל</t>
+          <t>בדיקת ייעודי קרקע + שיחה רלי</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5602,22 +5602,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ש.ב.א</t>
+          <t>מפעלי נשק</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>תביעה רמ"י</t>
+          <t>יוניסקופ</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>השלמת חוות דעת ושיחה אברבוך - תיקונים למודד</t>
+          <t>השלמת  מסמכים להקצאת קרקע</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5626,29 +5626,29 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>מבשרת ציון</t>
+          <t>עין יהב</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>בדיקות משפטיות</t>
+          <t>בדיקת מסמכי חברה תאגיד ועסקאות קודמות</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5657,29 +5657,29 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>מפעלי נשק</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>חניון רוטשילד</t>
+          <t>יוניסקופ</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>תיקונים לטיוטא</t>
+          <t>מרחב צפון רמ"י לקידום הקצאת הקרקע</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5688,14 +5688,14 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>תחנת שורק</t>
+          <t>צליל החורש</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>קריאת החלטת שמאית מחוזית + שיחה דרור</t>
+          <t>מרחב צפון פגישה ליאב לצורך קבלת הליך קודם ושיחה אסף</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5719,29 +5719,29 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>גבעוני</t>
+          <t>כפיר דהן</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>הארכת חכירה</t>
+          <t>כדורי</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>שוטף מול דפנה</t>
+          <t>מרחב צפון לענין רישומים</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5750,29 +5750,29 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>אקרשטיין</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>חלקה 68</t>
+          <t>רישום זכויות</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>תיקונים לטיוטא ושיחה יאיר</t>
+          <t>מרחב צפון (חלי) להשלמת העברת הזכויות</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5781,29 +5781,29 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>עקיבא איגר</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>רוכשים</t>
+          <t>קרית שמונה</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>טיפול ברישום ה"א</t>
+          <t>פגישה מרחב צפון חלי + ליאב לתיקון שטח החוזה</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5812,29 +5812,29 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ינושבסקי</t>
+          <t>גורדון 37</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>אבן גבירול</t>
+          <t>פינוי בינוי</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>טיפול במשכנתאות</t>
+          <t>פגישת זום וטיוטת מכתב לרה"ע</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5843,29 +5843,29 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>נייר חדרה</t>
+          <t>ש.ב.ה.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>חלקה 70</t>
+          <t>פרויקט עומר</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>מסמכים לרישום פרצלציה</t>
+          <t>שיחות בענין מכירת מניות וקרקע</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -5874,29 +5874,29 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>25.2.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>צליל החורש</t>
+          <t>מבשרת ציון</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ביקור במרחב צפון לקבלת תשריטים נוספים ומסמכי תביעה</t>
+          <t>בדיקת שטחים בהיתרי בניה קודמים</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -5905,29 +5905,29 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>25.2.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>ש.ב.ה.</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>קרית שמונה</t>
+          <t>חברת נוסטרו</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>מרחב צפון לצורך תיקון שטח חוזה</t>
+          <t>טיוטת הסכם לייסוד חברה</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5936,29 +5936,29 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>25.2.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>יוני סקופ</t>
+          <t>ש.ב.א</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>הקצאת קרקע</t>
+          <t>תביעה רמ"י</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ביקור במרחב צפון לקידום הבקשה</t>
+          <t>השלמת חוות דעת - תיקונים למודד</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -5967,29 +5967,29 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>4.5</v>
+        <v>0.75</v>
       </c>
       <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>25.2.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>אקרשטיין</t>
+          <t>מלכה רובין</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>העברת זכויות</t>
+          <t>נשר</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>מרחב צפון לקידום התיק</t>
+          <t>פגישה במשרד</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -5998,29 +5998,29 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>25.2.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>אודי שגב</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>תביעה למפקח</t>
+          <t>היטלים</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>תיקונים לכתב תביעה + שיחת ועידה ענת ויעל</t>
+          <t>שיחה רוית לענין הצעה דניאל</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6029,29 +6029,29 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>ש.ב.א</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>צליל החורש</t>
+          <t>תביעה רמ"י</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>שוטף</t>
+          <t>השלמת חוות דעת ושיחה אברבוך - תיקונים למודד</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6060,29 +6060,29 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>כפיר דהן</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>כדורי</t>
+          <t>מבשרת ציון</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>מכירת קרקע - טיפול בהשלמת עסקה קודמת</t>
+          <t>בדיקות משפטיות</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6091,29 +6091,29 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>משרד</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>כללי</t>
+          <t>חניון רוטשילד</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>דב הלפרן - בדיקת מסמכים והצעת שכ"ט</t>
+          <t>תיקונים לטיוטא</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6129,22 +6129,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>מבקשת ציון</t>
+          <t>תחנת שורק</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>כתב תביעה למפקחת תיקונים אחרונים והגשה</t>
+          <t>קריאת החלטת שמאית מחוזית + שיחה דרור</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6153,29 +6153,29 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>מפעלי נשק</t>
+          <t>גבעוני</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>יוניסקופ</t>
+          <t>הארכת חכירה</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>צירוף מדידות לרמ"י לעדכון הבקשה</t>
+          <t>שוטף מול דפנה</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6184,29 +6184,29 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>כפיר דהן</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>מכירת נכס</t>
+          <t>חלקה 68</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>תיקונים להסכם מכר כדורי + שיחות כפיר</t>
+          <t>תיקונים לטיוטא ושיחה יאיר</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6215,29 +6215,29 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>עקיבא איגר</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>אלבה</t>
+          <t>רוכשים</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>מסמ"ק אישורים העברה</t>
+          <t>טיפול ברישום ה"א</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6246,29 +6246,29 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>כפיר דהן</t>
+          <t>ינושבסקי</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>קצרין</t>
+          <t>אבן גבירול</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>השלמת עסקה ומסמכי בנק</t>
+          <t>טיפול במשכנתאות</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6277,29 +6277,29 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>27.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ש.ב.א</t>
+          <t>נייר חדרה</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>תביעה רמ"י</t>
+          <t>חלקה 70</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>תיקונים ובדיקות לחוות דעת מומחה (מודד)</t>
+          <t>מסמכים לרישום פרצלציה</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6308,29 +6308,29 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>27.02.2026</t>
+          <t>25.2.2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ירדן חובב</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>רכישת דירה</t>
+          <t>צליל החורש</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>התייחסות להסכם מכר</t>
+          <t>ביקור במרחב צפון לקבלת תשריטים נוספים ומסמכי תביעה</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -6339,29 +6339,29 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>25.2.2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>נחשון</t>
+          <t>קרית שמונה</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>טיפול בהעברת זכויות, שיחות חני, מסמכים לרמי</t>
+          <t>מרחב צפון לצורך תיקון שטח חוזה</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6370,29 +6370,29 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>25.2.2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>יוני סקופ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>צליל החורש</t>
+          <t>הקצאת קרקע</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>תיקון והקניית בעלות-שיחה אסף, בדיקת תשריטים, בדיקת היתרי בניה ותיק בניין בוועדה</t>
+          <t>ביקור במרחב צפון לקידום הבקשה</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6401,29 +6401,29 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>25.2.2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>אקרשטיין</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>עתירה מינהלית</t>
+          <t>העברת זכויות</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>תגובה לבקשת הצטרפות רוכשות</t>
+          <t>מרחב צפון לקידום התיק</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -6432,29 +6432,29 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>25.2.2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>עתירה מינהלית</t>
+          <t>תביעה למפקח</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>עתירה מתוקנת</t>
+          <t>תיקונים לכתב תביעה + שיחת ועידה ענת ויעל</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -6470,22 +6470,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>הר בלאן</t>
+          <t>צליל החורש</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>מכתב התראה לרוכשות</t>
+          <t>שוטף</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -6494,29 +6494,29 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>עודד מרגלית</t>
+          <t>כפיר דהן</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>רכישה בית הטקסטיל</t>
+          <t>כדורי</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>תיקון טיוטה ושיחה נווה</t>
+          <t>מכירת קרקע - טיפול בהשלמת עסקה קודמת</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -6525,29 +6525,29 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>משרד</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>בראבו</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>שיחת Zoom תיקון הסכם שכירות</t>
+          <t>דב הלפרן - בדיקת מסמכים והצעת שכ"ט</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -6556,14 +6556,14 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>מבשרת ציון</t>
+          <t>מבקשת ציון</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>שיחת ועידה בעניין הגשת ערר</t>
+          <t>כתב תביעה למפקחת תיקונים אחרונים והגשה</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -6587,29 +6587,29 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>0.75</v>
+        <v>3</v>
       </c>
       <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>אגירה</t>
+          <t>מפעלי נשק</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>בנק לאומי</t>
+          <t>יוניסקופ</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>שיחת Zoom בעניין מתווה לאשראי</t>
+          <t>צירוף מדידות לרמ"י לעדכון הבקשה</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -6625,22 +6625,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>שמשון זליג</t>
+          <t>כפיר דהן</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>הארכה תקופה</t>
+          <t>מכירת נכס</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ישיבה פנימית</t>
+          <t>תיקונים להסכם מכר כדורי + שיחות כפיר</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6649,29 +6649,29 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>סיגת</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>הארכת תקופה</t>
+          <t>אלבה</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ישיבה פנימית בדיקת מדידות ומכתב לרמי</t>
+          <t>מסמ"ק אישורים העברה</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6680,29 +6680,29 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>כפיר דהן</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>אופקים</t>
+          <t>קצרין</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>שיחה לירון זה העברת מסמכים בעניין הארכת תקופת חכירה חוזה שמעון אטיאס</t>
+          <t>השלמת עסקה ומסמכי בנק</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -6711,29 +6711,29 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>27.02.2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>נייר חדרה</t>
+          <t>ש.ב.א</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>הסכם מכרOPC</t>
+          <t>תביעה רמ"י</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ישיבה פנימית</t>
+          <t>תיקונים ובדיקות לחוות דעת מומחה (מודד)</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -6749,22 +6749,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>17.2.2036</t>
+          <t>27.02.2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>עקיבא איגר</t>
+          <t>ירדן חובב</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>רוכשים</t>
+          <t>רכישת דירה</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>טיפול במסירת דירה 6</t>
+          <t>התייחסות להסכם מכר</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -6773,7 +6773,7 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G205" t="inlineStr"/>
     </row>
